--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486895_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486895_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7355</v>
+        <v>8.436400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6833</v>
+        <v>6.2063</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0522</v>
+        <v>2.23</v>
       </c>
       <c r="G2" t="n">
         <v>4.7405</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4239</v>
+        <v>0.277</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6433</v>
+        <v>-0.1203</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2194</v>
+        <v>0.3973</v>
       </c>
       <c r="V2" t="n">
         <v>2.5975</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2528</v>
+        <v>6.8804</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9613</v>
+        <v>6.5889</v>
       </c>
       <c r="F3" t="n">
         <v>0.2916</v>
@@ -688,10 +688,10 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0891</v>
+        <v>0.5386</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5192</v>
+        <v>0.1084</v>
       </c>
       <c r="U3" t="n">
         <v>0.4302</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0911</v>
+        <v>5.9855</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0509</v>
+        <v>6.6785</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9598</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>5.9473</v>
@@ -766,13 +766,13 @@
         <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1046</v>
+        <v>-0.2102</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9804</v>
+        <v>-0.3527</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1243</v>
+        <v>0.1425</v>
       </c>
       <c r="V4" t="n">
         <v>1.0698</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8215</v>
+        <v>4.0771</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7177</v>
+        <v>4.2993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1038</v>
+        <v>-0.2223</v>
       </c>
       <c r="G5" t="n">
         <v>3.2876</v>
@@ -844,13 +844,13 @@
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9446</v>
+        <v>1.2001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0731</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.5455</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2705</v>
+        <v>2.2244</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4419</v>
+        <v>2.3959</v>
       </c>
       <c r="F6" t="n">
         <v>-0.1715</v>
@@ -922,10 +922,10 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9371</v>
+        <v>0.8911</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8363</v>
+        <v>0.7903</v>
       </c>
       <c r="U6" t="n">
         <v>0.1008</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4258</v>
+        <v>1.2768</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5279</v>
+        <v>0.5865</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8979</v>
+        <v>0.6904</v>
       </c>
       <c r="G7" t="n">
         <v>0.5688</v>
@@ -1000,13 +1000,13 @@
         <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6516</v>
+        <v>0.5027</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4333</v>
+        <v>0.4919</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2183</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6472</v>
+        <v>0.3961</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1366</v>
+        <v>1.2412</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4894</v>
+        <v>-0.8451</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4834</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4797</v>
+        <v>0.2286</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1704</v>
+        <v>0.275</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3093</v>
+        <v>-0.0464</v>
       </c>
       <c r="V8" t="n">
         <v>0.2402</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6385999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7211</v>
+        <v>-0.6322</v>
       </c>
       <c r="G9" t="n">
         <v>0.6155</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4327</v>
+        <v>0.2838</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3294</v>
+        <v>0.2983</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1034</v>
+        <v>-0.0144</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1619</v>
+        <v>-1.0293</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1948</v>
+        <v>-0.2994</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9671</v>
+        <v>-0.7299</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0642</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0977</v>
+        <v>0.0349</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4416</v>
+        <v>0.337</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5393</v>
+        <v>-0.3021</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6657</v>
+        <v>-1.2194</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3001</v>
+        <v>1.5093</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9659</v>
+        <v>-2.7287</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8815</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.189</v>
+        <v>0.6353</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2249</v>
+        <v>-0.0156</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4139</v>
+        <v>0.651</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9285</v>
+        <v>-2.5404</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8912</v>
+        <v>-1.4142</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0373</v>
+        <v>-1.1262</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0419</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8547</v>
+        <v>1.2427</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0149</v>
+        <v>0.4919</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8397</v>
+        <v>0.7508</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3573</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6144</v>
+        <v>-6.3303</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9104</v>
+        <v>-3.5966</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.704</v>
+        <v>-2.7336</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3579</v>
@@ -1468,13 +1468,13 @@
         <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0779</v>
+        <v>0.2063</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7169</v>
+        <v>-0.4031</v>
       </c>
       <c r="U13" t="n">
-        <v>0.639</v>
+        <v>0.6093</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7679</v>
@@ -1507,7 +1507,7 @@
         <v>24.9059</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.6706</v>
+        <v>-6.670500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>11.2463</v>
@@ -1546,13 +1546,13 @@
         <v>8.213699999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>5.830800000000001</v>
+        <v>5.8309</v>
       </c>
       <c r="T14" t="n">
-        <v>2.555499999999999</v>
+        <v>2.5558</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2751</v>
+        <v>3.2753</v>
       </c>
       <c r="V14" t="n">
         <v>0.1314000000000006</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3005</v>
+        <v>4.0572</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9196</v>
+        <v>6.338</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6191</v>
+        <v>-2.2809</v>
       </c>
       <c r="G15" t="n">
         <v>0.2117</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.948</v>
+        <v>-1.1914</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2516</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6965</v>
+        <v>-0.3582</v>
       </c>
       <c r="V15" t="n">
         <v>5.6529</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9725</v>
+        <v>1.3996</v>
       </c>
       <c r="E16" t="n">
         <v>1.6907</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.2911</v>
       </c>
       <c r="G16" t="n">
         <v>1.7845</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5985</v>
+        <v>-0.1714</v>
       </c>
       <c r="T16" t="n">
         <v>-0.6587</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0602</v>
+        <v>0.4873</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8295</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5997</v>
+        <v>-0.0419</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7521</v>
+        <v>3.1631</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3518</v>
+        <v>-3.2049</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0378</v>
+        <v>0.083</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7271</v>
+        <v>-0.993</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6893</v>
+        <v>1.0759</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7135</v>
+        <v>3.4995</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2141</v>
+        <v>0.474</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4994</v>
+        <v>3.0255</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7513</v>
+        <v>-3.4165</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9412</v>
+        <v>-1.467</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8101</v>
+        <v>-1.9495</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2306</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0386</v>
+        <v>-0.7286</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2692</v>
+        <v>-0.2517</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9474</v>
+        <v>1.0608</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9474</v>
+        <v>-0.3581</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.802</v>
+        <v>-0.3469</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6401</v>
+        <v>2.8567</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4421</v>
+        <v>-3.2036</v>
       </c>
       <c r="G18" t="n">
-        <v>0.083</v>
+        <v>-0.0378</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.993</v>
+        <v>-0.7271</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0759</v>
+        <v>0.6893</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4995</v>
+        <v>2.7135</v>
       </c>
       <c r="K18" t="n">
-        <v>0.474</v>
+        <v>0.2141</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0255</v>
+        <v>2.4994</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.4165</v>
+        <v>-2.7513</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.467</v>
+        <v>-0.9412</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9495</v>
+        <v>-1.8101</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7404</v>
+        <v>0.0223</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2516</v>
+        <v>0.1432</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4888</v>
+        <v>-0.121</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0608</v>
+        <v>-0.9474</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3581</v>
+        <v>-0.9474</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0726</v>
+        <v>-0.6141</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3249</v>
+        <v>2.5341</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3975</v>
+        <v>-3.1482</v>
       </c>
       <c r="G19" t="n">
         <v>1.3285</v>
@@ -1936,13 +1936,13 @@
         <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8993</v>
+        <v>-0.4408</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4225</v>
+        <v>-0.2133</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4768</v>
+        <v>-0.2275</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2965</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6382</v>
+        <v>-1.7755</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.43</v>
+        <v>-1.4156</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2082</v>
+        <v>-0.3599</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5397</v>
+        <v>-0.622</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2845</v>
+        <v>-0.9799</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2552</v>
+        <v>0.3579</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4798</v>
+        <v>-1.1016</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4798</v>
+        <v>-0.4832</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0599</v>
+        <v>0.4796</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8047</v>
+        <v>-0.4967</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2552</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4826</v>
+        <v>-0.3855</v>
       </c>
       <c r="T20" t="n">
-        <v>1.631</v>
+        <v>-0.1086</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1483</v>
+        <v>-0.2769</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3491</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1877</v>
+        <v>-2.8362</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3194</v>
+        <v>-2.3654</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8683</v>
+        <v>-0.4708</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8927</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6524</v>
+        <v>0.0039</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1698</v>
+        <v>0.1238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5175</v>
+        <v>-0.12</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3581</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4135</v>
+        <v>-2.9824</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.834</v>
+        <v>-1.6852</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5796</v>
+        <v>-1.2972</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.622</v>
+        <v>-1.5397</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9799</v>
+        <v>-1.2845</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3579</v>
+        <v>-0.2552</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1016</v>
+        <v>-0.4798</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4832</v>
+        <v>-0.4798</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4796</v>
+        <v>-1.0599</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4967</v>
+        <v>-0.8047</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.2552</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R22" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0235</v>
+        <v>0.1385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.527</v>
+        <v>0.3757</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4966</v>
+        <v>-0.2373</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1829</v>
+        <v>-4.0303</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7277</v>
+        <v>0.4139</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9106</v>
+        <v>-4.4442</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1636</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5433</v>
+        <v>-0.3041</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2907</v>
+        <v>-0.6045</v>
       </c>
       <c r="U23" t="n">
-        <v>0.834</v>
+        <v>0.3005</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7063</v>
+        <v>-4.2739</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0946</v>
+        <v>-1.7808</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6117</v>
+        <v>-2.4932</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5688</v>
@@ -2326,13 +2326,13 @@
         <v>0.4107</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3429</v>
+        <v>-0.9105</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7246</v>
+        <v>-0.4108</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6183</v>
+        <v>-0.4997</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9053</v>
+        <v>-5.3962</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7066</v>
+        <v>-3.079</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1987</v>
+        <v>-2.3172</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8294</v>
@@ -2404,13 +2404,13 @@
         <v>0.4107</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.726</v>
+        <v>-0.2169</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9881</v>
+        <v>-0.3605</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2621</v>
+        <v>0.1435</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7072000000000001</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.2352</v>
+        <v>-16.8406</v>
       </c>
       <c r="E26" t="n">
-        <v>6.670500000000002</v>
+        <v>6.670500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.9058</v>
+        <v>-23.5112</v>
       </c>
       <c r="G26" t="n">
         <v>-11.2463</v>
@@ -2482,16 +2482,16 @@
         <v>7.1869</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.8309</v>
+        <v>-4.4362</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2754</v>
+        <v>-3.2755</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.5557</v>
+        <v>-1.161</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1313000000000004</v>
+        <v>-0.1313000000000009</v>
       </c>
       <c r="W26" t="n">
         <v>7.5522</v>
